--- a/actual_df.xlsx
+++ b/actual_df.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UG2, UG1, OG2, OG3</t>
+          <t>OG3, UG2, UG1, OG2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 7.939, 11.947</t>
+          <t>11.947, -8.2, -3.78, 7.939</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1, 2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1224, 1225, 1226, 1227</t>
+          <t>1219, 1227, 1228, 1229</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -594,12 +594,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OG2, OG3, UG2, UG1, EG, OG1</t>
+          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.939, 11.947, -8.2, -3.78, 0.0, 2.998</t>
+          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -615,12 +615,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E, 1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97</t>
+          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1219, 1220, 1221, 1222</t>
+          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS, 3Q30KcAwrFjgFId43DWY8P</t>
+          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1217, 1218, 1228</t>
+          <t>1220, 1221, 1222</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>97.874376</v>
+        <v>97.87437599999998</v>
       </c>
       <c r="L4" t="n">
         <v>39.08309449999999</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY, 0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1223, 1232, 1233, 1234</t>
+          <t>1225, 1226, 1234, 1235</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OG3, EG</t>
+          <t>EG, OG3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>0.0, 11.947</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 2smUqi2i10zRE_diOVjJhu, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2, 0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1235, 1236, 1237, 1240, 1241, 1242, 1243, 1244, 1247, 1248, 1249, 1250</t>
+          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>784.1024639999999</v>
+        <v>784.1024640000001</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>693.2650894999999</v>
+        <v>693.2650895</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN, 2MZESDDfb379fB261rIbnR</t>
+          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1251, 1257, 1258</t>
+          <t>1252, 1253, 1259</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC, 3vSADXkCf9CehgpLlu0Bds</t>
+          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1229, 1230, 1231, 1238, 1239</t>
+          <t>1230, 1231, 1232, 1233, 1240</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1264, 1265</t>
+          <t>1265, 1266</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR, 1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1271, 1273, 1274, 1275</t>
+          <t>1271, 1272, 1275, 1276</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UG2, OG1</t>
+          <t>OG1, UG2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-8.2, 2.998</t>
+          <t>2.998, -8.2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj, 1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1273, 1278</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1276, 1282</t>
+          <t>1277, 1282</t>
         </is>
       </c>
       <c r="I45" t="n">

--- a/actual_df.xlsx
+++ b/actual_df.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.939</t>
+          <t>__pivot_7.94</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.947</t>
+          <t>__pivot_11.948</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OG3, UG2, UG1, OG2</t>
+          <t>UG2, UG1, OG2, OG3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.947, -8.2, -3.78, 7.939</t>
+          <t>-8.2, -3.78, 7.94, 11.948</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
+          <t>24xm6C08LB6PmPlweCGB8I, 0zR70dM_L5hgHRsQfW3Yo7, 1jaqyoTjT5Bhtkj1U9RyUu, 3yI4yvxYX9aBv$Jk3GB$dy</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1219, 1227, 1228, 1229</t>
+          <t>1202, 1203, 1204, 1205</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -594,12 +594,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
+          <t>OG1, OG2, OG3, UG2, UG1, EG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
+          <t>2.998, 7.94, 11.948, -8.2, -3.78, 0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -615,12 +615,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
+          <t>3Hh_lnoOjFseiPP$fBJdTk, 2P3Mbts9P06BZqiOxGDRsK, 39ETwZKMDAou$vKVot7pYG, 0WugxlnUz8xx2oGJ_ePbye, 1TuiyJHazFPP354k0XGOop, 049y1zqcb029syIWXEZkws</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
+          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
+          <t>0flQ6A_KT1au1P6tc3jqMc, 2F6s1tVBjDqQjhbB3E6WYb, 1ob0Dr3Tb3me5ixnzVhldr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1220, 1221, 1222</t>
+          <t>1194, 1195, 1196</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>97.87437599999998</v>
+        <v>101.688451</v>
       </c>
       <c r="L4" t="n">
-        <v>39.08309449999999</v>
+        <v>42.893664</v>
       </c>
       <c r="M4" t="n">
-        <v>58.7912815</v>
+        <v>58.794787</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
+          <t>3lSeJHANz4JwuuWWVWxbUH, 1s_RuZ0k90YAlXWhJ4lnX8, 3W2HgVPjj8sgJOb9kc$BUn, 3W8P9$rMX2_fA9sfb6fwqp</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1225, 1226, 1234, 1235</t>
+          <t>1200, 1201, 1209, 1210</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>62.2703145</v>
+        <v>61.5559585</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>54.69261700000001</v>
+        <v>53.978261</v>
       </c>
       <c r="N5" t="n">
         <v>7.5776975</v>
@@ -828,12 +828,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -899,12 +899,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>0wQhe8bif1LOoZtbl2gXny</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0, 11.947</t>
+          <t>0.0, 11.948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
+          <t>0HX_qt1yzF3xKWplASPhYe, 2qXFUIy2T3SBxq9lBM4xHo, 2RrGEvz4H6O8oYwW_ERzQ6, 1AENlAVbf0FPNqAceD_OOg, 0eDs_7T5r34RBessIb8ALy, 2KTKdUnXz3EAT3eZQsBIVW, 1dm6hXA1TAHxySfbOH_SuE, 3Ko5GwjxPFa8wWHDHgsYet, 0bj3cexLz16A$8LPJ5vRgB, 2CKlKmb3L8if01dRSHZkQk, 3VSDX0a6j5R9Sc3ExLWrsf, 1DAsWzcd53mxYOR7lJYiHX</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
+          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>784.1024640000001</v>
+        <v>801.9748285000001</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>693.2650895</v>
+        <v>693.3113715</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>90.8373745</v>
+        <v>108.663457</v>
       </c>
     </row>
     <row r="10">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>11.948, 0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>2jDi0spfj5xugCuK32MU8B, 1JP2teRZzAKhVlWoAk44Gi, 0cuCI57f5FDx6c5xjTH_wt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1252, 1253, 1259</t>
+          <t>1227, 1228, 1235</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>880.1147865</v>
+        <v>878.8663225</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>252.4451035</v>
+        <v>251.195758</v>
       </c>
     </row>
     <row r="11">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>3sBsqaQPb0euZE5Csd1V40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>0owNcgsrLCORAeZymoLxMZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
+          <t>367VhQ1U19B8v9mWQKmOzz, 2Hxz6DXsT92vehhFG6_ShJ, 38tAZDumv6$hnRXN0FwtYj, 2vghzoGT51TxNQvOAAv0j4, 2rIGmJBcz82eOKIU2HIoRF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1230, 1231, 1232, 1233, 1240</t>
+          <t>1206, 1207, 1208, 1215, 1216</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>0a48Ih65rFx8QfDnXMMhEl</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2jn0CO4WT6agpI_e3theVz</t>
+          <t>30_jhjUID1lOEnoZkbwPlR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0R6CzIVUf9Xg$xY9ZGMPOI</t>
+          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0mgHCA5Bj2q8PGPshAJwdu</t>
+          <t>2EdAa2vnvDwv$K313aI9nH</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2q$FhMpurDpQLxyHcG7QMH</t>
+          <t>0snplPWT179OZgXqJkFdam</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0lrhQ1hBL3UB9wu$bziAIW</t>
+          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15q5B8t2H1jOLW$YLJTSCd</t>
+          <t>3QuKuIVNvEDebBjhENRHdp</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1PXOCrKLD2ohK81bqcw5L8</t>
+          <t>1nHVq1BLj3N83VoxI$QAiV</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>37pvr1fmPFoPR8VqDaFSaH</t>
+          <t>1xAkayK$92b8rEYvsI7ddA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0x9I5spTf0W8z7GhPCk1ky</t>
+          <t>3tE0xz5ivFbule77FUWYT7</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2VOStX3MjEzAywBgrc2Ymz</t>
+          <t>2b761ZbMf7OQyYTjBYwlqS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1K1FlaQx1EExBCUKfCbQFS</t>
+          <t>2TkX3v9lLDHfNhAwV_173q</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>0bebBo2BjBix6YQ7lpTjg5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY, 2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>3P24pHOeX7huTaoUa46vgT, 0OAGNaNgv3wwzf3ckQ_KTm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1265, 1266</t>
+          <t>1241, 1242</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>3EFA13Ox1F58pYx6_i5NyU</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>220mi7GG59YuA9V0nhWv8f, 1CV6oaRyn1HQP8tN4myNln, 2JYUQcEU93zwiGeMtni83Z, 2O9cNxLZXB48ei75HpXuVM, 2E_TZJZ7r4DgKH0p0YQJl8, 1AmWYBKrzAYQ$BPe2iH8In</t>
+          <t>11rtg$OHHCQgjPenPfbWHc, 1IKxMLTg96xBLZwOLJkOep, 2lJbeNWPr69PR6Bv8eHLx5, 0sM00mZHr6DOEYTFqh$IrG, 0rjMKvNtzAnefNaYJ97j52, 0qFk07a55D6POPpcM5bCmf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1309, 1311, 1317, 1324, 1329, 1333</t>
+          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3885.43503</v>
+        <v>3885.5616805</v>
       </c>
       <c r="L32" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="M32" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="N32" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="O32" t="n">
         <v>607.3553475</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2h61zMFo5AJAPRusVng_Xn, 1ocReKPMH6yQHek4DHBHWe, 1WVo1W$JrFBwJk1Ud33P2_, 2tu7qWjqT2KwS8C7vq8SbN, 2rXFWc8jX9X9uAiF4mg4_c, 1xVbGem8z8Yw7KMlDD7tyl, 29mRuo3Gj2kAoruOaOpQPk, 2UYbzXfWX4jeekEZZounLu, 2iqV3awXnFaPEu0T7HAtp4, 2HDdALzov8sOiati08LIYR, 191C_eUqLBjwUYQYjuyzbJ</t>
+          <t>2g7lHgM9fCfeWFLbqCROTN, 2TjpIVE3fEjf2yeWwF5tbt, 37U7QqRiD3K8YpI0EDvqEG, 3Phqv9RFv0aPLT5D_Im9QT, 2CTrriW1D4XfbevcRhL0D$, 3ue0$unPz0uux7AwL1STF3, 0BPV577Cv2qOXbm$_0BLlX, 0D49X8G8b21vMvV9fI6DYy, 3QbhoocVL16heqVtso3nIe, 1vS9xL68j7QRd7X5GTAvLE, 1MeUygKbr5gwqhdLnI1$fr</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1307, 1308, 1310, 1314, 1315, 1316, 1321, 1322, 1323, 1328, 1332</t>
+          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2738,16 +2738,16 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>5484.661963</v>
+        <v>5484.879056999999</v>
       </c>
       <c r="L33" t="n">
-        <v>1893.5052305</v>
+        <v>1893.5763265</v>
       </c>
       <c r="M33" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="N33" t="n">
-        <v>1280.054072</v>
+        <v>1280.172307</v>
       </c>
       <c r="O33" t="n">
         <v>615.1939470000001</v>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2rnYpcA2j5ORd2uupGEvG0</t>
+          <t>1elxkk8h12l8VI66SES48s</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21ftMaN2H3x9V_1Iuv7_Lz</t>
+          <t>2jQqxIN7D0G9XrN3psKCHB</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0kB0A2S5z5auQg3$i3qAjO</t>
+          <t>0SfLsfaY1DQQexHNkqpPq8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="L36" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3fS1w73ELCBRUIqHWvP3$z, 2FQ8B6_JP08wqgDmUUSwZn</t>
+          <t>25qvKAslv4su4AGnfPnQAy, 0$R0qHln98kepMxkmwzDXO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1283, 1284</t>
+          <t>1259, 1260</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>7.9612265</v>
+        <v>8.0182985</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>1KAZImcajE19VMZ2urkS9A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>0p4XPibzXDmfYuHdDNQKoi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1F3Fkq$vj7GQErmS_ow7lc, 1acftYr2jDufGYUUZLoAmB</t>
+          <t>2DRzef4hn3IgIiLgkhkHE9, 2EaietiEbAIPhvSO2Cvy$b</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1269, 1270</t>
+          <t>1245, 1246</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
+          <t>2_ozTiGP19wxfIiizV$YDP, 1hrw6SBSX5_xz0kjcf$lQq, 3MbScePwXCG951Z0r4L0yN, 3YWB1QD45A0ffgE_grSlSK</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1271, 1272, 1275, 1276</t>
+          <t>1247, 1248, 1250, 1251</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3360,12 +3360,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1MPw1r9hv6$h6AZYdCPJK4</t>
+          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>0fphzOn3z3ffzYnIZDfkRZ, 3$MWY95kL37xnSaojxj3cW</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1273, 1278</t>
+          <t>1252, 1253</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c, 3fqw08GKT8VB$WT6lvspWB</t>
+          <t>1mK10My2H1Jf6TH2FFyNJl, 0v8vKsFUHEhuGCI94TqyuL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1277, 1282</t>
+          <t>1257, 1258</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2goFLwB6DCTwDTgbAWEEIH, 0d65XwDRr8KPZICzeqHSW5</t>
+          <t>2gsiWFr2TB1AHTbv7ojX6m, 3jgApaggT6VOj2drGLqhV$</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1301, 1302</t>
+          <t>1277, 1278</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0WJ65NDaH54RWZcOZo2hFz, 0DQARhKmnCX83BGrsfeEgq</t>
+          <t>0L$CPopvL2ng78uaCkxmd2, 2R0Ko1_rT45gQWRWnSw8Rh</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1303, 1304</t>
+          <t>1279, 1280</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1wnl70Hcf4J91aH6kWoQ5w</t>
+          <t>2pxOd96v91mxlwof2bdwwu</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3542EqJCz3j9Eu7i7LwKQI</t>
+          <t>2RQb_YuIX0cupTG8njrqa5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1H1NJxt1P4dhBGOFdbv$N4</t>
+          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1xCUaRipzEBRjcRGOUa__w</t>
+          <t>0ydbChVXH5YeiOECwP0lP5</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3gQV9bpHv7NfVbjzlui7Lj</t>
+          <t>3865N6dr5D2QZmKnsV5UjA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0x5OAt7GXB6Rq0gRG_tICL</t>
+          <t>2dCF9Z2NrCiPs79T_2XETx</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1nbtU4bcH2MeFbv04K7ZN2</t>
+          <t>3th3YBjLPEbgeAFO8BnVLM</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0CmilJIZr6B8RyG4QW7HcZ</t>
+          <t>2V_TDJQGX5u9IXI55MWQFM</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1dO_bQkdz9nwDyTkTE7ib2, 1Bex$LLBz14RGCBVd_3SHQ, 0s4lbBN6v2wQ56baFu8aCK, 19fOi9h4H1XBR85Agg_fkE, 1YjQd29ADBdhHAaWT8IdQR, 2yWWAdHcT0Ee9Cxo9n9g3E</t>
+          <t>0XnoVHZ5b7YeZWNQ2bXPFm, 3aH$lMb654_u$4SW_WvFAN, 14l9pM3sL8xfYz1mvXCNWG, 0hYc3lmMH2T91sw96db3JM, 0pnXM2gsT77R5nDFj8mzSx, 3hhMFg80L1LfBHM_a3hr7A</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1313, 1319, 1320, 1325, 1326, 1331</t>
+          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>164.6158945</v>
+        <v>166.5463805</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -4372,16 +4372,16 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="O56" t="n">
-        <v>50.5339195</v>
+        <v>51.266701</v>
       </c>
       <c r="P56" t="n">
-        <v>57.0922475</v>
+        <v>57.619245</v>
       </c>
       <c r="Q56" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
     </row>
     <row r="57">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3S19U$d1v2EAwMe1MFmPkg, 0cZezKqu94ovlQgVTxGUP9, 0Dg5sNnYTBWwyKrJUXkFTO, 3eXcdEMUX3XuwJXhU1bBiW</t>
+          <t>1CcwMqeXT8UesKx8nLd6OD, 1MQDEFDcX439MvQ3uigCM$, 2$k1ahqBDFJPjWMBdR8WtC, 3r8c5tGbPC_fDRkxzKA81G</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1312, 1318, 1327, 1330</t>
+          <t>1288, 1294, 1303, 1306</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>27.30605</v>
+        <v>41.80292</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4435,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="O57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="P57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
     </row>
   </sheetData>

--- a/actual_df.xlsx
+++ b/actual_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,32 +486,32 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_-8.2</t>
+          <t>__pivot_-9.25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_-3.78</t>
+          <t>__pivot_-6.4</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>__pivot_-3.6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>__pivot_0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>__pivot_2.998</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.94</t>
+          <t>__pivot_3.65</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.948</t>
+          <t>__pivot_7.65</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UG2, UG1, OG2, OG3</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 7.94, 11.948</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -548,16 +548,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24xm6C08LB6PmPlweCGB8I, 0zR70dM_L5hgHRsQfW3Yo7, 1jaqyoTjT5Bhtkj1U9RyUu, 3yI4yvxYX9aBv$Jk3GB$dy</t>
+          <t>3R2xljncLFrwUcVRqrVWQB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1202, 1203, 1204, 1205</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>56.0238215</v>
+        <v>40.81309</v>
       </c>
       <c r="L2" t="n">
-        <v>10.7493655</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>18.0784765</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -580,10 +580,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>13.6486625</v>
+        <v>40.81309</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.547317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -594,12 +594,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OG1, OG2, OG3, UG2, UG1, EG</t>
+          <t>-3. Geschoss, -2. Geschoss, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.998, 7.94, 11.948, -8.2, -3.78, 0.0</t>
+          <t>-9.25, -6.4, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -615,12 +615,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3Hh_lnoOjFseiPP$fBJdTk, 2P3Mbts9P06BZqiOxGDRsK, 39ETwZKMDAou$vKVot7pYG, 0WugxlnUz8xx2oGJ_ePbye, 1TuiyJHazFPP354k0XGOop, 049y1zqcb029syIWXEZkws</t>
+          <t>0QGjRpssrCEf62jJYAXlKy, 2179hTJDz4qe$lLgQDGjs5, 2bfZjgao1Dv97JNyykkr_m, 0oLpxmuLrD3vpEnaHL8ZBj, 1qKOcF2ODCce7VLD9rsXEH, 2PljEqQLzB2ubXqkxHG$np</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
+          <t>1203, 1204, 1205, 1206, 1207, 1208</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -632,25 +632,25 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>41.376825</v>
+        <v>30.033636</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3140405</v>
+        <v>15.671564</v>
       </c>
       <c r="M3" t="n">
-        <v>2.312567</v>
+        <v>6.229276</v>
       </c>
       <c r="N3" t="n">
-        <v>29.7644175</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3140405</v>
+        <v>2.710932</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3140405</v>
+        <v>2.710932</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.357719</v>
+        <v>2.710932</v>
       </c>
     </row>
     <row r="4">
@@ -661,12 +661,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UG2, UG1</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-8.2, -3.78</t>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -686,16 +686,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0flQ6A_KT1au1P6tc3jqMc, 2F6s1tVBjDqQjhbB3E6WYb, 1ob0Dr3Tb3me5ixnzVhldr</t>
+          <t>0zMGxe1BH1TxrCrIVjVasx, 0r$EqdMpj3RfiqlR4uoawX, 3Iu9ARz1n06eCv$RLYK8mN, 1PBVp6jL50d9XpS2BSM7Q3, 3dOvSe5UX79wzz5B1UL_ow, 0xFnUORwv85B7hCDyxBIe3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1194, 1195, 1196</t>
+          <t>1209, 1210, 1211, 1212, 1213, 1214</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -703,25 +703,25 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>101.688451</v>
+        <v>74.875981</v>
       </c>
       <c r="L4" t="n">
-        <v>42.893664</v>
+        <v>8.5472</v>
       </c>
       <c r="M4" t="n">
-        <v>58.794787</v>
+        <v>8.5472</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8.5472</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>14.820174</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14.820174</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>19.594033</v>
       </c>
     </row>
     <row r="5">
@@ -732,12 +732,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EG, UG1</t>
+          <t>EG, 1. Geschoss, OG, -3. Geschoss, -2. Geschoss, UG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0, -3.78</t>
+          <t>0.0, 3.65, 7.65, -9.25, -6.4, -3.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -757,16 +757,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3lSeJHANz4JwuuWWVWxbUH, 1s_RuZ0k90YAlXWhJ4lnX8, 3W2HgVPjj8sgJOb9kc$BUn, 3W8P9$rMX2_fA9sfb6fwqp</t>
+          <t>3bagB9kcv85vun_VdjVODa, 0at7qB32n7xwYKBY7SyXY4, 3_LTi1Z9TDWRmn1Acr_AH5, 01SSfasGf4gu$W_Yordu28, 2_slEYTbH0uwkjArsmzKBU, 31kIq08c57IhP5TEcyAIRZ, 0IHz2m9ov5YgNzsWm0g81F, 2rdVzlqnn3yOJdDWB7Lf3k, 3YxZGBMHn7qO_DYBivbzUS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1200, 1201, 1209, 1210</t>
+          <t>1215, 1216, 1217, 1218, 1219, 1222, 1223, 1224, 1225</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -774,31 +774,31 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>61.5559585</v>
+        <v>199.928687</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>46.315696</v>
       </c>
       <c r="M5" t="n">
-        <v>53.978261</v>
+        <v>52.826958</v>
       </c>
       <c r="N5" t="n">
-        <v>7.5776975</v>
+        <v>41.415856</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>27.22131</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>19.352178</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>12.796689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>ASP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
+          <t>3nn4tnKqz1a9xEhA8QGB9a</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -841,11 +841,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aussenbereich_ALL</t>
+          <t>Aussenbereich_ASP</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>396.6236325</v>
+        <v>17.459065</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>396.6236325</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>17.459065</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -869,22 +869,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG, 1. Geschoss</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.65, 3.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -899,24 +899,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
+          <t>2FfePHlQb1H8ONBzgx2KjG, 0Gz4j4MRX6XvLzeg45njs3, 3CxQ1gWQ51uhZIBxj8axdL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1221, 1229, 1230</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aussenbereich_ASP</t>
+          <t>Aussenbereich_BUF</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29.849794</v>
+        <v>501.804965</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -925,22 +925,22 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>29.849794</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>234.720456</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>267.084509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AVF</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0wQhe8bif1LOoZtbl2gXny</t>
+          <t>3xQxX0PgLFyhEfNxq5ExSw</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -983,11 +983,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aussenbereich_AVF</t>
+          <t>Aussenbereich_PAA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12.9937485</v>
+        <v>937.550941</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>12.9937485</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>937.550941</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1011,22 +1011,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EG, OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0, 11.948</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1041,24 +1041,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0HX_qt1yzF3xKWplASPhYe, 2qXFUIy2T3SBxq9lBM4xHo, 2RrGEvz4H6O8oYwW_ERzQ6, 1AENlAVbf0FPNqAceD_OOg, 0eDs_7T5r34RBessIb8ALy, 2KTKdUnXz3EAT3eZQsBIVW, 1dm6hXA1TAHxySfbOH_SuE, 3Ko5GwjxPFa8wWHDHgsYet, 0bj3cexLz16A$8LPJ5vRgB, 2CKlKmb3L8if01dRSHZkQk, 3VSDX0a6j5R9Sc3ExLWrsf, 1DAsWzcd53mxYOR7lJYiHX</t>
+          <t>0PEqNgC89CshH_53Wkr3$b</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aussenbereich_BUF</t>
+          <t>Aussenbereich_PAG</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>801.9748285000001</v>
+        <v>255.723749</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1067,32 +1067,32 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>693.3113715</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>255.723749</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>108.663457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>VEL_L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OG3, EG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11.948, 0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1112,24 +1112,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2jDi0spfj5xugCuK32MU8B, 1JP2teRZzAKhVlWoAk44Gi, 0cuCI57f5FDx6c5xjTH_wt</t>
+          <t>1jQMCRdaTCAxYCwHT9ZTYe</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1227, 1228, 1235</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aussenbereich_PAA</t>
+          <t>Aussenbereich_VEL_L</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>878.8663225</v>
+        <v>7.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>627.6705645</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>251.195758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>VEL_S</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3sBsqaQPb0euZE5Csd1V40</t>
+          <t>3p8gJcXfrDbeARU6GGAIAQ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1196,11 +1196,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Aussenbereich_PAG</t>
+          <t>Aussenbereich_VEL_S</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>73.5662785</v>
+        <v>15.21</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>73.5662785</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>15.21</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1224,54 +1224,54 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>AUF_G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Betreuung</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0owNcgsrLCORAeZymoLxMZ</t>
+          <t>25$VtZP153yhSX5bRPwPaU, 3xYlykRhjAeBm0JhwdmY7E</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1288, 1296</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Aussenbereich_PAK</t>
+          <t>Betreuung_AUF_G</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>295.8120275</v>
+        <v>76.96207899999999</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>295.8120275</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>76.96207899999999</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1295,42 +1295,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>AUF_M</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Betreuung</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
+          <t>2VjXtZBPn7$QycJJ85z80D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Aussenbereich_PPA</t>
+          <t>Betreuung_AUF_M</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>17.289957</v>
+        <v>69.02808</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1351,13 +1351,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>17.289957</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>69.02808</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1366,54 +1366,54 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>BLB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Betreuung</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>367VhQ1U19B8v9mWQKmOzz, 2Hxz6DXsT92vehhFG6_ShJ, 38tAZDumv6$hnRXN0FwtYj, 2vghzoGT51TxNQvOAAv0j4, 2rIGmJBcz82eOKIU2HIoRF</t>
+          <t>38MauQ3FTFVx5MNVVenPpY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1206, 1207, 1208, 1215, 1216</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Aussenbereich_UUF</t>
+          <t>Betreuung_BLB</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>389.1074575</v>
+        <v>16.617348</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1422,13 +1422,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>389.1074575</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>16.617348</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VEL_L</t>
+          <t>KUC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Betreuung</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0a48Ih65rFx8QfDnXMMhEl</t>
+          <t>2uPY50Sib749o5WIuFGRpT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1480,11 +1480,11 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Aussenbereich_VEL_L</t>
+          <t>Betreuung_KUC</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5.20168</v>
+        <v>42.49605</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.20168</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>42.49605</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1508,7 +1508,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEL_S</t>
+          <t>KUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1523,27 +1523,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Betreuung</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
+          <t>3aRQdr1dX0NRYyWhsc5L_w</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Aussenbereich_VEL_S</t>
+          <t>Betreuung_KUE</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>18.206341</v>
+        <v>6.174564</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1564,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>18.206341</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.174564</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AUF_G</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30_jhjUID1lOEnoZkbwPlR</t>
+          <t>3ZfLIBOpn5IObGi$psA5G_</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1622,11 +1622,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Betreuung_AUF_G</t>
+          <t>Betreuung_KUL</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>71.548801</v>
+        <v>4.58035</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>71.548801</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.58035</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AUF_M</t>
+          <t>KUW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
+          <t>0IlZmRlo50QOL9BoyqRs1A</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1693,11 +1693,11 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Betreuung_AUF_M</t>
+          <t>Betreuung_KUW</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>53.9113785</v>
+        <v>5.26419</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1706,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>53.9113785</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.26419</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1721,17 +1721,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BLB</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2EdAa2vnvDwv$K313aI9nH</t>
+          <t>3unooK3Gb53wP5rjxO9DU1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1764,11 +1764,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Betreuung_BLB</t>
+          <t>Betreuung_MEN</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>17.5731125</v>
+        <v>73.128405</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>73.128405</v>
       </c>
       <c r="P19" t="n">
-        <v>17.5731125</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KUC</t>
+          <t>VOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss, EG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65, 0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1822,24 +1822,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0snplPWT179OZgXqJkFdam</t>
+          <t>1Dv0nT0wvAc96JfBjMbO63, 1wXQLSsdzAo8tX0e9rPv_0, 1dy$wbFnHA$AUPXvByysgw, 2TMrDToPv0s8QlXMbvZv0x</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1283, 1290, 1291, 1292</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Betreuung_KUC</t>
+          <t>Betreuung_VOR</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>64.21340600000001</v>
+        <v>107.915895</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1848,13 +1848,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>64.21340600000001</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>53.954019</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>53.961876</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1863,22 +1863,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KUE</t>
+          <t>WCD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
+          <t>29dhkfqqj1VOZgFMDYpCg3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1906,11 +1906,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Betreuung_KUE</t>
+          <t>Betreuung_WCD</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6.9409425</v>
+        <v>6.189876</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1919,13 +1919,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.9409425</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1934,22 +1934,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>WCH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3QuKuIVNvEDebBjhENRHdp</t>
+          <t>1qu0RAu_5Bi9v6wMjwq2hO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Betreuung_KUL</t>
+          <t>Betreuung_WCH</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4.44016</v>
+        <v>6.189876</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.44016</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KUW</t>
+          <t>WCR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>EG, 1. Geschoss</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0, 3.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2035,24 +2035,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1nHVq1BLj3N83VoxI$QAiV</t>
+          <t>0binosZSD2TRmMGGbm$Riz, 0wQ3tggsr80BEk7K$paN07</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1278, 1279</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Betreuung_KUW</t>
+          <t>Betreuung_WCR</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>7.189814</v>
+        <v>5.866476</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2061,13 +2061,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>7.189814</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.933238</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.933238</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2076,27 +2076,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MEN</t>
+          <t>HTR_E</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Betreuung</t>
+          <t>Funktionsfläche</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1xAkayK$92b8rEYvsI7ddA</t>
+          <t>1zlPnmNiz1DPGCdwjs_BAh</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2119,11 +2119,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Betreuung_MEN</t>
+          <t>Funktionsfläche_HTR_E</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>72.32068099999999</v>
+        <v>6.229276</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>72.32068099999999</v>
+        <v>6.229276</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2147,27 +2147,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VOR</t>
+          <t>HTR_L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG, UG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.65, -3.6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Betreuung</t>
+          <t>Funktionsfläche</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2177,24 +2177,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3tE0xz5ivFbule77FUWYT7</t>
+          <t>1gy1MO$xP7XRrROZz1e_bn, 2r3VzFO2P8BhGedOcYmqyS, 05phPmber0Agf4IgoU6h56, 2shfm9PYTCFQzCvcxPOOdY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1231, 1238, 1239, 1240</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Betreuung_VOR</t>
+          <t>Funktionsfläche_HTR_L</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>123.8381265</v>
+        <v>214.391424</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>123.8381265</v>
+        <v>198.723156</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2212,33 +2212,33 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>15.668268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WCD</t>
+          <t>HTR_S</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Betreuung</t>
+          <t>Funktionsfläche</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2b761ZbMf7OQyYTjBYwlqS</t>
+          <t>329ZR9gIvFJgW$Yp42rcBC</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2261,20 +2261,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Betreuung_WCD</t>
+          <t>Funktionsfläche_HTR_S</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2.8944635</v>
+        <v>33.822831</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.8944635</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>33.822831</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2287,171 +2287,147 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WCH</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NNF</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Betreuung</t>
-        </is>
-      </c>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>GFA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2TkX3v9lLDHfNhAwV_173q</t>
+          <t>32xUYb6gT8ZucWxfAPPPgB, 1gidodw_DBO9zIqA4I4Tyi, 3WZJVz6859o9dSIhC80w61, 1$oL8Hh4H33QJDNcRaLaPg, 3ASPZ5Wb51Rw0CSOTH9tVP, 0iesInyHDFsviRu9$LiyeK, 13q4zSvG9DdwoWJkGCk_fu, 3o72QFQvr7lf7nGhb1DBtF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1295, 1300, 1307, 1308, 1313, 1314, 1317, 1323</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Betreuung_WCH</t>
+          <t>GrossArea</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2.719245</v>
+        <v>5479.670978</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1287.12523</v>
       </c>
       <c r="M27" t="n">
-        <v>2.719245</v>
+        <v>1287.12523</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1325.614241</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>541.0999609999999</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>522.619173</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>516.087143</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HTR_E</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>FF</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Funktionsfläche</t>
-        </is>
-      </c>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>USERDEFINED</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0bebBo2BjBix6YQ7lpTjg5</t>
+          <t>20NpxpK69BFusUiDDRtf10, 3E$tswQAPCsPCgMRjNrHsH, 1qrbHXBMX2yRhjue$7geb$, 1eupe3juT8aftOlJ9hg638, 2ZCe634fb8iAvhVJag1Fcc, 0FxKGVCyz3Of58MYD8Mv3b, 2ul_LbSif04OvKs5CQ_IKY, 0ZW72VIr95rvOTTkPJLq6U, 2sTcAT2vnE1hVbGM9h6Tnm, 1wAuqP15H2LOxT7LD11zVk, 2gWaEX$Kj1hO1wo$Ao7Kks, 21YsDo5uzBdg3lkyBC3bVL, 3dgN8ScwjAL8S2O$LS6ZfP, 3G6rr_NhPEYvBraTj5LRYF, 3JmSL5c0j0Y8vrCOJ5enu8, 3biGXOu7f9lB4VQJQ9hvUL, 1rr$OnbQ96LAXyyNlpar0j, 2HEec9CxzEQh9FJ8XfDnu9, 3$b34kgN18YQ50N33qhfdq, 0sC5YvQerEDBnRusKtCUG4, 2xViyMp9n4eg8BzzxxAxL1, 2Ej$q3hWLA$AALtqSSgISc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1293, 1294, 1297, 1298, 1299, 1301, 1302, 1303, 1304, 1305, 1306, 1309, 1310, 1311, 1312, 1315, 1316, 1318, 1319, 1320, 1321, 1322</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Funktionsfläche_HTR_E</t>
+          <t>GrossVolume</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>25.280915</v>
+        <v>10718.382495</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2574.25046</v>
       </c>
       <c r="M28" t="n">
-        <v>25.280915</v>
+        <v>2574.25046</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3079.153133</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>969.3224289999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>545.0024430000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>976.4035699999998</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HTR_K</t>
+          <t>AGH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UG2, UG1</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-8.2, -3.78</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Funktionsfläche</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2461,12 +2437,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3P24pHOeX7huTaoUa46vgT, 0OAGNaNgv3wwzf3ckQ_KTm</t>
+          <t>2t_chHHxX9fBLHfnDfn8L9, 2dYgk4XDnFFRRPb42IS4Tb</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1241, 1242</t>
+          <t>1259, 1260</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2474,17 +2450,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Funktionsfläche_HTR_K</t>
+          <t>Hausdienst_AGH</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>81.8638385</v>
+        <v>408.501664</v>
       </c>
       <c r="L29" t="n">
-        <v>68.07347249999999</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>13.790366</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2496,33 +2472,33 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>408.501664</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HTR_L</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Funktionsfläche</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2532,12 +2508,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3EFA13Ox1F58pYx6_i5NyU</t>
+          <t>0g0QzkYn50YeACUxcPqf9T</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2545,14 +2521,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Funktionsfläche_HTR_L</t>
+          <t>Hausdienst_CON</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>130.4597315</v>
+        <v>12.085796</v>
       </c>
       <c r="L30" t="n">
-        <v>130.4597315</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2561,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>12.085796</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2573,27 +2549,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HTR_S</t>
+          <t>GRP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Funktionsfläche</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2603,12 +2579,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
+          <t>0zkT_iaZXCl80nJ7Y9EKl4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2616,14 +2592,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Funktionsfläche_HTR_S</t>
+          <t>Hausdienst_GRP</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>38.861445</v>
+        <v>23.562948</v>
       </c>
       <c r="L31" t="n">
-        <v>38.861445</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2635,144 +2611,168 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>23.562948</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RRG</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UG2, UG1, EG, OG1, OG2, OG3</t>
+          <t>1. Geschoss, UG, EG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>3.65, -3.6, 0.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NNF</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hausdienst</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GFA</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11rtg$OHHCQgjPenPfbWHc, 1IKxMLTg96xBLZwOLJkOep, 2lJbeNWPr69PR6Bv8eHLx5, 0sM00mZHr6DOEYTFqh$IrG, 0rjMKvNtzAnefNaYJ97j52, 0qFk07a55D6POPpcM5bCmf</t>
+          <t>3wTnr2v4rAteZQ5bF5K2_M, 2j5JNLySbAteSlc$brVcCs, 2JNSHBJa53Sua8Pc8lc41H</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
+          <t>1262, 1266, 1267</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>GrossArea</t>
+          <t>Hausdienst_RRG</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3885.5616805</v>
+        <v>44.366531</v>
       </c>
       <c r="L32" t="n">
-        <v>946.7966155</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>944.3288025000001</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>635.473241</v>
+        <v>25.387835</v>
       </c>
       <c r="O32" t="n">
-        <v>607.3553475</v>
+        <v>9.489348</v>
       </c>
       <c r="P32" t="n">
-        <v>607.3728175</v>
+        <v>9.489348</v>
       </c>
       <c r="Q32" t="n">
-        <v>144.2348565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AGS</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UG2, UG1, EG, OG1, OG2, OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HNF</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sportbereich</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USERDEFINED</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2g7lHgM9fCfeWFLbqCROTN, 2TjpIVE3fEjf2yeWwF5tbt, 37U7QqRiD3K8YpI0EDvqEG, 3Phqv9RFv0aPLT5D_Im9QT, 2CTrriW1D4XfbevcRhL0D$, 3ue0$unPz0uux7AwL1STF3, 0BPV577Cv2qOXbm$_0BLlX, 0D49X8G8b21vMvV9fI6DYy, 3QbhoocVL16heqVtso3nIe, 1vS9xL68j7QRd7X5GTAvLE, 1MeUygKbr5gwqhdLnI1$fr</t>
+          <t>0CAa9Ma5fEHAjsub3tn7O2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>GrossVolume</t>
+          <t>Sportbereich_AGS</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>5484.879056999999</v>
+        <v>16.617348</v>
       </c>
       <c r="L33" t="n">
-        <v>1893.5763265</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>944.3288025000001</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1280.172307</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>615.1939470000001</v>
+        <v>16.617348</v>
       </c>
       <c r="P33" t="n">
-        <v>607.3728175</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>144.2348565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>GRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2792,33 +2792,33 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1elxkk8h12l8VI66SES48s</t>
+          <t>2MkuFBa9j3ePTZR6et6RVm, 0L1$lPM39FEOrqxv4xuzey</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1250, 1251</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Hausdienst_CON</t>
+          <t>Sportbereich_GRL</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>11.070615</v>
+        <v>31.119685</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>31.119685</v>
       </c>
       <c r="N34" t="n">
-        <v>11.070615</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -2833,17 +2833,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GRP</t>
+          <t>GSA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2863,30 +2863,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2jQqxIN7D0G9XrN3psKCHB</t>
+          <t>2rdOLwb$X52u_kCvUQVX3F, 35xWWY93XABfSkaS7vI23K, 1Ri5H0T4f54A_siIEhqmyK, 1RbjKB6vbE7gqDdeJ9nwPe</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1254, 1255, 1256, 1257</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Hausdienst_GRP</t>
+          <t>Sportbereich_GSA</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>11.5049595</v>
+        <v>185.735414</v>
       </c>
       <c r="L35" t="n">
-        <v>11.5049595</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>185.735414</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2904,27 +2904,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HRR</t>
+          <t>RHW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0SfLsfaY1DQQexHNkqpPq8</t>
+          <t>2kzklfMtXAHh4tqI4eVVZB</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Hausdienst_HRR</t>
+          <t>Sportbereich_RHW</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>24.251362</v>
+        <v>14.753575</v>
       </c>
       <c r="L36" t="n">
-        <v>24.251362</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>14.753575</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -2975,17 +2975,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RRG</t>
+          <t>RRS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>-3. Geschoss</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3005,30 +3005,30 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25qvKAslv4su4AGnfPnQAy, 0$R0qHln98kepMxkmwzDXO</t>
+          <t>0OF33YtIv4Hx1G$D83kBWw</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1259, 1260</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Hausdienst_RRG</t>
+          <t>Sportbereich_RRS</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>8.0182985</v>
+        <v>20.059019</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>20.059019</v>
       </c>
       <c r="M37" t="n">
-        <v>3.639574</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.3787245</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3046,22 +3046,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>VSR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3071,29 +3071,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1KAZImcajE19VMZ2urkS9A</t>
+          <t>0c0SRnRBf3BBLeCiaKjt2p, 0U$47L9U1EhBqNR_6mg9tg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1246, 1247</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sportbereich_AGS</t>
+          <t>Sportbereich_VSR</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>14.9977755</v>
+        <v>4.89984</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>14.9977755</v>
+        <v>4.89984</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3117,17 +3117,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>WAL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss, OG, -3. Geschoss, -2. Geschoss, UG, EG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65, 7.65, -9.25, -6.4, -3.6, 0.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3142,63 +3142,63 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0p4XPibzXDmfYuHdDNQKoi</t>
+          <t>3eRDR1539DfAyqNphQzEld, 0o_Vc6NJL42u6QeIg$vfUv, 3gR2dIIQv1K87prBYZma2s, 1JZ2sCz4j0vBHYKD6E6EZ9, 0ZeDtOxF9B1BRh5BeNaVTG, 19HwThHHbEQhAJY3thvaQZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1236, 1237, 1241, 1242, 1243, 1244</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sportbereich_ESP</t>
+          <t>Sportbereich_WAL</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>34.1596555</v>
+        <v>78.881229</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>13.148786</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>13.148786</v>
       </c>
       <c r="N39" t="n">
-        <v>34.1596555</v>
+        <v>13.148786</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>13.144957</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>13.144957</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>13.144957</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRL</t>
+          <t>WCK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-3. Geschoss, EG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-9.25, 0.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2DRzef4hn3IgIiLgkhkHE9, 2EaietiEbAIPhvSO2Cvy$b</t>
+          <t>1GupYPuB9CruRMuqndzcqi, 2PXzDaDKDBjOeh2XaUMhzK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1245, 1246</t>
+          <t>1284, 1285</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3231,23 +3231,23 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sportbereich_GRL</t>
+          <t>Sportbereich_WCK</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>31.359346</v>
+        <v>20.353308</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>14.163432</v>
       </c>
       <c r="M40" t="n">
-        <v>31.359346</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3259,17 +3259,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>WCM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-3. Geschoss, EG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-9.25, 0.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3289,36 +3289,36 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2_ozTiGP19wxfIiizV$YDP, 1hrw6SBSX5_xz0kjcf$lQq, 3MbScePwXCG951Z0r4L0yN, 3YWB1QD45A0ffgE_grSlSK</t>
+          <t>3fFbnlvNn6yBCGAa2MPByn, 0Nx1PuXgb0a8CG7aDO$ArL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1247, 1248, 1250, 1251</t>
+          <t>1286, 1287</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sportbereich_GSA</t>
+          <t>Sportbereich_WCM</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>169.608867</v>
+        <v>20.359151</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>14.169275</v>
       </c>
       <c r="M41" t="n">
-        <v>169.608867</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3330,22 +3330,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RHW</t>
+          <t>WKR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3360,33 +3360,33 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
+          <t>3D5GVSrbL438sA_MPBDGbw, 2EYxBkIxv2Vf417tC4kF_B</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1248, 1249</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sportbereich_RHW</t>
+          <t>Sportbereich_WKR</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>13.502395</v>
+        <v>7.012924</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>7.012924</v>
       </c>
       <c r="N42" t="n">
-        <v>13.502395</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -3401,27 +3401,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RRS</t>
+          <t>BSO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2.998</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
+          <t>3lmnlW15D2Wugg6LXVgUh$</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3444,11 +3444,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sportbereich_RRS</t>
+          <t>Unterricht_BSO</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>11.810404</v>
+        <v>16.610202</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3460,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>11.810404</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>16.610202</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3472,27 +3472,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>LMZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UG2, OG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-8.2, 2.998</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0fphzOn3z3ffzYnIZDfkRZ, 3$MWY95kL37xnSaojxj3cW</t>
+          <t>0YH2RK9kLDqwvfXM8yftVB, 1CHulNgsD11gfOQj$248Mm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1252, 1253</t>
+          <t>1273, 1274</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3515,14 +3515,14 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sportbereich_SGR</t>
+          <t>Unterricht_LMZ</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>179.438013</v>
+        <v>31.441863</v>
       </c>
       <c r="L44" t="n">
-        <v>89.857005</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>89.581008</v>
+        <v>31.441863</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3543,17 +3543,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SPH</t>
+          <t>LOG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UG2, OG1</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-8.2, 2.998</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3573,27 +3573,27 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1mK10My2H1Jf6TH2FFyNJl, 0v8vKsFUHEhuGCI94TqyuL</t>
+          <t>2i1NFgikHFlA_lWjrfBTUV</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1257, 1258</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sportbereich_SPH</t>
+          <t>Unterricht_LOG</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>926.76099</v>
+        <v>34.083666</v>
       </c>
       <c r="L45" t="n">
-        <v>463.376039</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3602,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>463.384951</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>34.083666</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3614,27 +3614,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WCK</t>
+          <t>MKZ_K</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3644,39 +3644,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2gsiWFr2TB1AHTbv7ojX6m, 3jgApaggT6VOj2drGLqhV$</t>
+          <t>3fb_XRdw1BteQSKn8BY9E6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sportbereich_WCK</t>
+          <t>Unterricht_MKZ_K</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>15.627722</v>
+        <v>16.610202</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>9.246236</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>16.610202</v>
       </c>
       <c r="P46" t="n">
-        <v>6.381486</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3685,27 +3685,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WCM</t>
+          <t>MKZ_M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3715,39 +3715,39 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0L$CPopvL2ng78uaCkxmd2, 2R0Ko1_rT45gQWRWnSw8Rh</t>
+          <t>33qUnSF8j9cPczPAl_STyj</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1279, 1280</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sportbereich_WCM</t>
+          <t>Unterricht_MKZ_M</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>15.6001035</v>
+        <v>33.936144</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>11.0386675</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>33.936144</v>
       </c>
       <c r="P47" t="n">
-        <v>4.561436</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3756,27 +3756,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WKR</t>
+          <t>MZS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Unterricht</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2pxOd96v91mxlwof2bdwwu</t>
+          <t>0YwbNN_Wv11OqMxI4D7nsg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3799,23 +3799,23 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sportbereich_WKR</t>
+          <t>Unterricht_MZS</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>3.934619</v>
+        <v>90.623125</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.934619</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>90.623125</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3827,17 +3827,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BSO</t>
+          <t>TAR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11.948</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2RQb_YuIX0cupTG8njrqa5</t>
+          <t>3K19Ry5FvE$O9E_6DflNxN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3870,11 +3870,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Unterricht_BSO</t>
+          <t>Unterricht_TAR</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>17.564029</v>
+        <v>51.55713</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3889,562 +3889,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>51.55713</v>
       </c>
       <c r="Q49" t="n">
-        <v>17.564029</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LMZ</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NNF</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Unterricht_LMZ</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>20.323617</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>20.323617</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LOG</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>OG3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>11.948</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0ydbChVXH5YeiOECwP0lP5</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Unterricht_LOG</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>35.5960265</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>35.5960265</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MKZ_K</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>OG3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>11.948</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>3865N6dr5D2QZmKnsV5UjA</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Unterricht_MKZ_K</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>17.564029</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>17.564029</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MKZ_M</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>OG3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>11.948</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2dCF9Z2NrCiPs79T_2XETx</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Unterricht_MKZ_M</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>35.517629</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>35.517629</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MZS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>3th3YBjLPEbgeAFO8BnVLM</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Unterricht_MZS</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>90.066202</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>90.066202</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>TAR</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>OG2</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Unterricht</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2V_TDJQGX5u9IXI55MWQFM</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Unterricht_TAR</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>51.768942</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>51.768942</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>aTRH</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>EG, OG1, OG2, OG3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0XnoVHZ5b7YeZWNQ2bXPFm, 3aH$lMb654_u$4SW_WvFAN, 14l9pM3sL8xfYz1mvXCNWG, 0hYc3lmMH2T91sw96db3JM, 0pnXM2gsT77R5nDFj8mzSx, 3hhMFg80L1LfBHM_a3hr7A</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>aTRH</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>166.5463805</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>17.082447</v>
-      </c>
-      <c r="O56" t="n">
-        <v>51.266701</v>
-      </c>
-      <c r="P56" t="n">
-        <v>57.619245</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>40.5779875</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>aTRHA</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>EG, OG1, OG2, OG3</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1CcwMqeXT8UesKx8nLd6OD, 1MQDEFDcX439MvQ3uigCM$, 2$k1ahqBDFJPjWMBdR8WtC, 3r8c5tGbPC_fDRkxzKA81G</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1288, 1294, 1303, 1306</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>aTRHA</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>41.80292</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="O57" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="P57" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>10.45073</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/actual_df.xlsx
+++ b/actual_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="286">
   <si>
     <t>LongName</t>
   </si>
@@ -49,16 +49,22 @@
     <t>sum_Qto_SpaceBaseQuantities.NetFloorArea</t>
   </si>
   <si>
-    <t>__pivot_-8.0</t>
-  </si>
-  <si>
-    <t>__pivot_-4.0</t>
-  </si>
-  <si>
-    <t>__pivot_0.0</t>
-  </si>
-  <si>
-    <t>__pivot_4.0</t>
+    <t>__pivot_-0.5</t>
+  </si>
+  <si>
+    <t>__pivot_-4.5</t>
+  </si>
+  <si>
+    <t>__pivot_14.9</t>
+  </si>
+  <si>
+    <t>__pivot_3.0</t>
+  </si>
+  <si>
+    <t>__pivot_6.4</t>
+  </si>
+  <si>
+    <t>__pivot_9.3</t>
   </si>
   <si>
     <t>VRF</t>
@@ -67,6 +73,9 @@
     <t>ALL</t>
   </si>
   <si>
+    <t>ASP</t>
+  </si>
+  <si>
     <t>BUF</t>
   </si>
   <si>
@@ -76,18 +85,15 @@
     <t>PAA</t>
   </si>
   <si>
+    <t>PAG</t>
+  </si>
+  <si>
     <t>PAK</t>
   </si>
   <si>
-    <t>PPA</t>
-  </si>
-  <si>
     <t>UUF</t>
   </si>
   <si>
-    <t>VEL_L</t>
-  </si>
-  <si>
     <t>AUF_G</t>
   </si>
   <si>
@@ -100,30 +106,69 @@
     <t>KUC</t>
   </si>
   <si>
+    <t>KUE</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>KUW</t>
+  </si>
+  <si>
     <t>MEN</t>
   </si>
   <si>
+    <t>RKU</t>
+  </si>
+  <si>
+    <t>VOR</t>
+  </si>
+  <si>
+    <t>WCD</t>
+  </si>
+  <si>
+    <t>WCH</t>
+  </si>
+  <si>
     <t>WCR</t>
   </si>
   <si>
     <t>HTR_E</t>
   </si>
   <si>
+    <t>HTR_K</t>
+  </si>
+  <si>
     <t>HTR_L</t>
   </si>
   <si>
+    <t>HTR_S</t>
+  </si>
+  <si>
     <t>AGH</t>
   </si>
   <si>
     <t>CON</t>
   </si>
   <si>
-    <t>KUE - KUL - KUW - RKU</t>
+    <t>GRP</t>
+  </si>
+  <si>
+    <t>HRR</t>
+  </si>
+  <si>
+    <t>RRG</t>
   </si>
   <si>
     <t>LUF</t>
   </si>
   <si>
+    <t>AVF</t>
+  </si>
+  <si>
+    <t>TRHa</t>
+  </si>
+  <si>
     <t>AGS</t>
   </si>
   <si>
@@ -148,9 +193,6 @@
     <t>SPH</t>
   </si>
   <si>
-    <t>VSR</t>
-  </si>
-  <si>
     <t>WCK</t>
   </si>
   <si>
@@ -181,57 +223,105 @@
     <t>TAR</t>
   </si>
   <si>
-    <t>Floor, Basement, Groundfloor, Basement 2</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>Groundfloor</t>
-  </si>
-  <si>
-    <t>Groundfloor, Floor</t>
-  </si>
-  <si>
-    <t>Basement</t>
-  </si>
-  <si>
-    <t>Basement 2, Basement, Groundfloor, Floor</t>
-  </si>
-  <si>
-    <t>Basement 2, Basement</t>
-  </si>
-  <si>
-    <t>Basement 2</t>
-  </si>
-  <si>
-    <t>4.0, -4.0, 0.0, -8.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>0.0, 4.0</t>
-  </si>
-  <si>
-    <t>-4.0</t>
-  </si>
-  <si>
-    <t>-8.0, -4.0, 0.0, 4.0</t>
-  </si>
-  <si>
-    <t>-8.0, -4.0</t>
-  </si>
-  <si>
-    <t>-8.0</t>
+    <t>-1. Geschoss, 1. Geschoss</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>1. Geschoss</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 3.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, EG</t>
+  </si>
+  <si>
+    <t>4. Geschoss</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 2.OG, 3.OG, 4. Geschoss, EG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 2.OG, 3.OG, EG</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 2.OG, 3.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 2.OG</t>
+  </si>
+  <si>
+    <t>2.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 3.OG</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 2.OG, EG</t>
+  </si>
+  <si>
+    <t>3.OG</t>
+  </si>
+  <si>
+    <t>-4.5, 3.0</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>3.0, 9.3</t>
+  </si>
+  <si>
+    <t>-4.5</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5, 14.9, 3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5, 3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>-4.5, 6.4</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>-4.5, 3.0, 9.3</t>
+  </si>
+  <si>
+    <t>-0.5, 3.0, 6.4</t>
+  </si>
+  <si>
+    <t>9.3</t>
   </si>
   <si>
     <t>VF</t>
   </si>
   <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
     <t>HNF</t>
   </si>
   <si>
@@ -259,6 +349,9 @@
     <t>Hausdienst</t>
   </si>
   <si>
+    <t>Sonstige Umgebung</t>
+  </si>
+  <si>
     <t>Sportbereich</t>
   </si>
   <si>
@@ -277,256 +370,343 @@
     <t>USERDEFINED</t>
   </si>
   <si>
-    <t>3FJla_fc5AowlVR7K0V9Jn, 0Ox5WtWrHCdvUeqlAzpmsA, 2KzcsUtHfBYemvn9UyzE81, 2s0L327tr6VRsn315VFcv4, 3ape7LX1X19Pl3XG73pAjv, 1qyhUqqr5EOARgC$yiuTqD, 2bBI1elkj0Oek9cmG$Q3Ma</t>
-  </si>
-  <si>
-    <t>0Qq$waI0D4tgESdrUp3c1O, 12gKHTtNfFmekuay$mdDom</t>
-  </si>
-  <si>
-    <t>1y7wXEg0X4jefW$q9l4Sws, 1PK9Ey0Zn5ivXyO02tNPnE, 1PGhHlbO9DiepinQf6hwYs, 2bQtO28tjCYgFpzLJoIk5N, 25xRd4zeb6FQai$4dR8fLo</t>
-  </si>
-  <si>
-    <t>33c9HIJ6n9FOg9jQ10e7XW</t>
-  </si>
-  <si>
-    <t>0h1Q_MKjL9qhO9xPZHQEC0, 2SYYV19HfFMg$eemP5gsSh, 3DvTiD3qjCGQNIzPLShWzK</t>
-  </si>
-  <si>
-    <t>0emDOihfX32QTN4LjMxx$8</t>
-  </si>
-  <si>
-    <t>3p6Crgcl11owBHhQgVm2dt</t>
-  </si>
-  <si>
-    <t>1j9ARi4v99MOAXxrEKQnIY, 0mQ1OQ2KbCoe4O8U7o7ZGC, 1c0iJwEOv0axC7QIHzNVe4, 0E7k058g59EPHY8fcst31G, 2Y3tOWW6rAHQictn8s8MM1, 095A0lJ1b0POgbye2cXhbz, 1m5RyVkwD45uqUi5nGK8Om, 0T04Yc55TAz9Ex6LYJ5ttH</t>
-  </si>
-  <si>
-    <t>3GA2fBeGn3QxvfaWJ4nNbE</t>
-  </si>
-  <si>
-    <t>0OmUU7RRTBVOUuHb_tcrS8</t>
-  </si>
-  <si>
-    <t>2Pk7nRyp98sP$yjORrs$b2</t>
-  </si>
-  <si>
-    <t>3loFfwTqb4YOQ9Wj6CnMQT</t>
-  </si>
-  <si>
-    <t>1t1lbS9dr2XheriClmXJFP</t>
-  </si>
-  <si>
-    <t>2AD3ezC5T7OfiQqUeNinT_</t>
-  </si>
-  <si>
-    <t>0ojKeiJj18hQAeKsi3MCUz</t>
-  </si>
-  <si>
-    <t>08oscw6nX9IPLbM6vUne$H</t>
-  </si>
-  <si>
-    <t>1UvvnA5DLAd8fqE7Om3NFZ</t>
-  </si>
-  <si>
-    <t>1WNqKfJ7f4fg0RlNTYk9rK, 32NtxuewD39fPwhjc9G7eh, 1RFHFul31DC8qTzrd9evSS, 3aq0p0uGDAjBIR7qH9wVOd, 3v6IM9aIvFKOBlWhGX2vX8, 0Apkm4xBn9tRUr_fB_H6Lb, 3w$H7yTfXDeuHQIh$eqjLR, 09V2p$ADT3k87hS8HnQXg5</t>
-  </si>
-  <si>
-    <t>2LFkdj2QnCduMSHvYtBipx, 1PFzIrJErEG84kwBn$OxXw, 0euxUbDfP52Qc_j3rPztSY, 31VZCub5f7XAYMvBGmRa5R, 0$_Sn4eLfFGA$RreVOUGOn, 2h5TsfB6rCe9bDQwyy1rq1, 3c_NATrkH3xB08nykkf1Lp, 3XaHP2zmrA3vDOSMe7Irpy, 1eGXVG4HX18uWobSy1k1CA, 0JaBps47PAgPOMaWJ0meX6, 0zE$h5Uhv1PuMt9aKeH0dj, 3v1q2JbnbEqRpjcqWTGNDb, 07dmsc3UH1DAxq9qZltZyB, 2MHNF1f5P0ixnGPhqeigZs, 2lZvvG_1r7Xfo0Vce_7ZXd, 1DXdSaBCbDqA0q8AMlEGVL</t>
-  </si>
-  <si>
-    <t>3otq55wJT9YgG0D8Q2B8_2</t>
-  </si>
-  <si>
-    <t>1mx6e_dIr8_uSnqKdiufRK</t>
-  </si>
-  <si>
-    <t>1ht0JSji12JRAqLAuzG0Zp</t>
-  </si>
-  <si>
-    <t>0RzL8$X8L06gFg8eO$_Qsh, 3rV0oQhib3YgzVr4_uUQ6a</t>
-  </si>
-  <si>
-    <t>3N8W7vx_5DmOt4Avylvrgn</t>
-  </si>
-  <si>
-    <t>1j_jbAQEPEpAcj1Xi8a79K</t>
-  </si>
-  <si>
-    <t>290YmwkjP5aQCW4Epq0Pza, 3OWT1c0sTFxOwz95LItwwg</t>
-  </si>
-  <si>
-    <t>0BpaR0hHz7VAcCz87UWf1K, 0z1SwaP1HC9R$loNNu$fXb, 316WPdNFDAwRWNuCi6Dhu5, 1_XORWbpXEAvr3naAPATha</t>
-  </si>
-  <si>
-    <t>2we13nKQzDmPaBLsZSFqB4</t>
-  </si>
-  <si>
-    <t>2U9ujtpOn898Rdakz4pgW4, 31rDDfYQL5G9RbBbj2wsQ2</t>
-  </si>
-  <si>
-    <t>19pgcqrjD5I8VmiiLq8sbk, 28vkS$9e5FMAxNzs8GvhIy</t>
-  </si>
-  <si>
-    <t>2w$DxGPXrCFAsMbQs2MCJk, 1L9ZCkaHDE6wCgAr7Iq7Xh</t>
-  </si>
-  <si>
-    <t>0iYUGTNL9BKeBLvk3nj8TR, 1idjNrKPv26Pz0EyIGwstp</t>
-  </si>
-  <si>
-    <t>1IVWxSbyD22fC6Q9EoQ8Y8</t>
-  </si>
-  <si>
-    <t>2VHM8Espn8duFOS$g8X3S4</t>
-  </si>
-  <si>
-    <t>2QUDBoj296Cvg94FJb02hF, 0MyIb3f256A9MTle5rK9tm</t>
-  </si>
-  <si>
-    <t>26sl1kLDDBMvf3KDMedOa9</t>
-  </si>
-  <si>
-    <t>3hQqkNfLH9gg4u7ntjHcbj</t>
-  </si>
-  <si>
-    <t>3mrWJ5d_DCSOTp9ongMy5V</t>
-  </si>
-  <si>
-    <t>2cMoz_61HBjRfJFK9Xuq2q</t>
-  </si>
-  <si>
-    <t>3ptVibDCT3s8$BeVgkWauO</t>
-  </si>
-  <si>
-    <t>304DRh$Br1bB8wCYHm8mJe</t>
-  </si>
-  <si>
-    <t>1qvE8w_nP6g8gbxkltALhk</t>
-  </si>
-  <si>
-    <t>976, 979, 980, 981, 982, 983, 986</t>
-  </si>
-  <si>
-    <t>1035, 1043</t>
-  </si>
-  <si>
-    <t>1030, 1031, 1032, 1033, 1038</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>1040, 1041, 1042</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>1020, 1021, 1025, 1026, 1027, 1028, 1029, 1034</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>984</t>
-  </si>
-  <si>
-    <t>1047, 1050, 1058, 1059, 1060, 1067, 1068, 1069</t>
-  </si>
-  <si>
-    <t>1045, 1046, 1048, 1049, 1052, 1053, 1054, 1055, 1056, 1057, 1061, 1062, 1063, 1064, 1065, 1066</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>977, 978</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>987</t>
-  </si>
-  <si>
-    <t>995, 996</t>
-  </si>
-  <si>
-    <t>998, 999, 1000, 1001</t>
-  </si>
-  <si>
-    <t>988</t>
-  </si>
-  <si>
-    <t>993, 994</t>
-  </si>
-  <si>
-    <t>1002, 1003</t>
-  </si>
-  <si>
-    <t>1004, 1005</t>
-  </si>
-  <si>
-    <t>989, 990</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>991, 992</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1007</t>
+    <t>EXTERNAL, INTERNAL</t>
+  </si>
+  <si>
+    <t>0p1lENSoT5JfYmbpsgfmRt, 0wCAq0jgHCYvksd553QSn5, 2TNi1nxkfFkABCIp_dod2V, 304Yc6LEnBPxWhkwUFRLGQ, 3_y_gVstb83QpahCzBUnsB</t>
+  </si>
+  <si>
+    <t>3xa830HAf5gu6oBd5CywNb</t>
+  </si>
+  <si>
+    <t>1iHyFgYW1BChl1fRzC2TFE</t>
+  </si>
+  <si>
+    <t>2NmoQFhlLD3RtSI7q$w3ip, 2fahcaiuj46uE3P_8bkPKG, 2ibyAWWwH8Ch2C7vVRPEvR</t>
+  </si>
+  <si>
+    <t>17TJN44C5AZPctiYS36OpO, 2FvWFmZEf8RfbMTC$V5m2H, 2yAKVjTsn0uxY4GHs5XEAc</t>
+  </si>
+  <si>
+    <t>0YKJ_UpPP6xAH7MASML2$y, 0kqhWa_T5A6QEWEt6g4nBS, 0vb4Up$vH6wPRM89uVviTL, 0wcPYvVLf1QRz72KfUk8C$, 1kUVSVJcb4PuHgCLOTTMNJ, 2as_cWSvj95QK73E_XtxJV</t>
+  </si>
+  <si>
+    <t>2V_ryaK7X7IQY8rAvTbMfZ</t>
+  </si>
+  <si>
+    <t>07IJJjJ0f7PhT6cQSEphQc, 0V7fc2fYLADwg3MDcCyASr</t>
+  </si>
+  <si>
+    <t>2WDktp3XT3JPFqlt$OaNaD, 2esnaMxAP7E8qRqN1wi0Qs</t>
+  </si>
+  <si>
+    <t>1_Nf_eVonClhcXh6bUIhI2, 35Hx_9doD7z9n_QX4p0J6E</t>
+  </si>
+  <si>
+    <t>3IGPSzI1D26OYVbQL8QXmx</t>
+  </si>
+  <si>
+    <t>3CVAz3qE5DZ8zKmeIUfmRY</t>
+  </si>
+  <si>
+    <t>07MMNyWPrBlvnheniAZbN0</t>
+  </si>
+  <si>
+    <t>2jrhBrM6b21wRrLKuK8w_l</t>
+  </si>
+  <si>
+    <t>07zVYpgibF1xUBmaROh$$F</t>
+  </si>
+  <si>
+    <t>1AQfPYknD0fvgE2OJ203Fd</t>
+  </si>
+  <si>
+    <t>0AiGclYXf2pR$I_JJBUEUK, 38JS_x8w53sAtZB3$O_E_I</t>
+  </si>
+  <si>
+    <t>375_S0Hb9BpO4Vb$kT7hv0</t>
+  </si>
+  <si>
+    <t>2$C3Bg_6v41BNFh4tE9iWE, 2bKvu8opn3aeaaHo3FCTYQ, 3aWIBLmun8xQwDeDkCsms8</t>
+  </si>
+  <si>
+    <t>1XEpW$cvD4BBIrutknz0Li</t>
+  </si>
+  <si>
+    <t>05ck$tPxf0ug8iCmNvdD42</t>
+  </si>
+  <si>
+    <t>1iMEAALTb7a84z5vd4yHSE</t>
+  </si>
+  <si>
+    <t>1A5PyTdLvFggyb7IseXr0g</t>
+  </si>
+  <si>
+    <t>1glaB34_X70u5uIK$zAIc2, 3lCvbxxlz0nvI4eYtaPNct</t>
+  </si>
+  <si>
+    <t>2_gmJsxJvCHAXbuuMm6MAf</t>
+  </si>
+  <si>
+    <t>26RDUdXLv59OaQSt7VWZGn</t>
+  </si>
+  <si>
+    <t>0uTdmZpQr689WLzyXoMPMw, 1MLcl8cWjE5fgGs30NdXgm, 2YtsbQ_8PBxAhEA067Et6q, 2xdqNP89f4ke2gkmAWzexq, 3A4uoXqxb5C91V0WTvsCXp, 3WQ5Nxw0TBu9NFehsPLqKO</t>
+  </si>
+  <si>
+    <t>0_bL9xRaL4E9haNI6$mny2, 1$SeO2fG98Jw2$_k3rvGgs, 1PZjNBwQrATR5Ih0UsqcP1, 1qcJDz_NbC5xuvMS8lIPUZ, 1tZBONVL1FFO0MgvG2xgWX, 2CmITZ0rX67gi8x8F0uM$W, 2Incpf6HvFPAp1ExMHJbHv, 2Iy9Hsskj46eQBgw77zsKk, 2S_2Kp2xXEEuNbwtOqdEUQ, 3Mb8fsOC19hhhkphmma5V_, 3WEQyxX5zCtRZzJcbMN6iH, 3gjySlsG181Byy84Ytg2R8, 3pGch8Bez9f8VMc$i961qz</t>
+  </si>
+  <si>
+    <t>2s6_0aRv9889e59zmDeZ6l</t>
+  </si>
+  <si>
+    <t>0$p2yq41j9ruEy6V6tIh2v</t>
+  </si>
+  <si>
+    <t>2KAYYodpPD29Ui4SHOaqvV</t>
+  </si>
+  <si>
+    <t>18ovLmE_v59vE2MWqJWWlV</t>
+  </si>
+  <si>
+    <t>0LTQh8B7X7SvC7KUiiThMD, 1PjFG3xAD0yvsi1rpU5$if</t>
+  </si>
+  <si>
+    <t>1cqwfrVO10XAAQoHwMWBY0</t>
+  </si>
+  <si>
+    <t>0Qt0xbz210ePk1ETgcTRAe</t>
+  </si>
+  <si>
+    <t>0A1FPOLpbDSRZQHbgifANJ, 0ggfX4ROvE$gn9oI2po6hs, 0iyXO7t2zBVAjFehekF44y, 0sYvMtXFvFog3SsZPbibSv, 0zaeuovYj4HxUQbxNDVVuv, 17H4UtdcH30x2aVWwiHzpl, 19yOQyJEn8wh5sF2LlSO8h, 1Cv_QD$SL3tAYxgT$2d4ki, 2MUujldmDF_hf6Kl51X1Hd, 2Vr3mF39f16Oqo$Lzh1x82, 3bqSUryV57I8lezJPgz9RY, 3fVc5k8UXBUuj626Ve2F8S</t>
+  </si>
+  <si>
+    <t>2ShMSTKej0vRXTBV2HRvE9, 2cphe79ET2RP1zKGpM43B$, 3vS9$ioef8ev_qzyK6NV6L</t>
+  </si>
+  <si>
+    <t>1ziUsWhzn78fM8rbtgkP3T, 3zEfxnCBj6sAxTBWhy8ur3</t>
+  </si>
+  <si>
+    <t>0Q9ijkiQX4WhhnplWe_zdJ</t>
+  </si>
+  <si>
+    <t>3KAORRhsnAKwP86D6sr$3l</t>
+  </si>
+  <si>
+    <t>0SsV_3mGL8jQnkPuwroY3_, 3TcJ$990X3ivnq$qgRm$vO</t>
+  </si>
+  <si>
+    <t>003gYzC8LEduA338bYwucG, 0TisxChxjEBOUhNCGFPe5W, 0_BHgmglj3egU7C5xU9ViK, 0oObqa8CrBxRX_rInOt3c9, 0tWf2kC1586uZ0sri7zb1n, 1I7IP$U65BCfKTkdnLbcd2, 1VzOtYuMDEhAu6QSpNDCN5, 1d8yru8NX6o90r$HjR_aRA, 1dFOwotOTCfAsAhSMBtTej, 1pD1pQ8dvCURhHWak1nEUO, 1w$b_g_$93zPxspdDWnPhI, 2ADk9oWpT7Ah0MjwZ8QsOz, 2v1Xk0MT1048VGbEtULKUb, 3$y1RDlEH0RRtkBIhMh7P2, 3GGqNyT7T26Qo_U3sVoYMy, 3JsInGZFTBEPodl2bEFnyx</t>
+  </si>
+  <si>
+    <t>2Xs6SIZyn3xvF3_RRaA6Fa</t>
+  </si>
+  <si>
+    <t>0M206jXKP8eAaUepdqB7iE, 3V9sbZj5LCafTPex$waLzL</t>
+  </si>
+  <si>
+    <t>0W4yXqkDzB5O81QntMj9c5, 280x3tfED1EOT34xdRY2ZA</t>
+  </si>
+  <si>
+    <t>1$RYaSg8X0JxDf6yNcAH30</t>
+  </si>
+  <si>
+    <t>1_HXy1qTTDahuLTlluTa95, 3gGcyYuafEPhCroukrmjZ7, 3iPsvIziH3_AeEtdPN$vau</t>
+  </si>
+  <si>
+    <t>0mqAnSSW1EmO318nABjLZj, 1TryAnXErCXw_zBNYqupuU, 3AFAWlkE99MgdF$DN0_GFR</t>
+  </si>
+  <si>
+    <t>0qfC$pra906wRpgxs$S$Wk, 1PUaeZ3ZrBmxeXjNjnOnHd</t>
+  </si>
+  <si>
+    <t>0vGnRSDojASeua7XxAW1bb</t>
+  </si>
+  <si>
+    <t>3mdc60Mwv2tPnYFvWNhknL</t>
+  </si>
+  <si>
+    <t>0f1Ttarxj3$OA$lHODYeRs</t>
+  </si>
+  <si>
+    <t>0s$ynE1pz43grKFhHey8dX</t>
+  </si>
+  <si>
+    <t>2UkroYiVTF1hfZ3bDpwLnM</t>
+  </si>
+  <si>
+    <t>39NjWXkNLEHOv8CGOj4lg8</t>
+  </si>
+  <si>
+    <t>0f1Q$uOUP7ovO4kZkr7IW_</t>
+  </si>
+  <si>
+    <t>1542, 1548, 1549, 1550, 1551</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>1623, 1629, 1630</t>
+  </si>
+  <si>
+    <t>1635, 1636, 1642</t>
+  </si>
+  <si>
+    <t>1631, 1632, 1633, 1637, 1638, 1639</t>
+  </si>
+  <si>
+    <t>1643</t>
+  </si>
+  <si>
+    <t>1640, 1641</t>
+  </si>
+  <si>
+    <t>1624, 1625</t>
+  </si>
+  <si>
+    <t>1620, 1621</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>1602, 1603</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>1613, 1614, 1615</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>1557, 1558</t>
+  </si>
+  <si>
+    <t>1552</t>
+  </si>
+  <si>
+    <t>1553</t>
+  </si>
+  <si>
+    <t>1649, 1655, 1657, 1659, 1662, 1665</t>
+  </si>
+  <si>
+    <t>1646, 1647, 1648, 1651, 1652, 1653, 1654, 1656, 1658, 1660, 1661, 1663, 1664</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>1589, 1594</t>
+  </si>
+  <si>
+    <t>1645</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>1535, 1536, 1537, 1538, 1539, 1540, 1541, 1543, 1544, 1545, 1546, 1547</t>
+  </si>
+  <si>
+    <t>1626, 1627, 1628</t>
+  </si>
+  <si>
+    <t>1618, 1619</t>
+  </si>
+  <si>
+    <t>1578</t>
+  </si>
+  <si>
+    <t>1555</t>
+  </si>
+  <si>
+    <t>1562, 1563</t>
+  </si>
+  <si>
+    <t>1565, 1566, 1567, 1568, 1569, 1570, 1571, 1572, 1573, 1574, 1575, 1576, 1577, 1579, 1580, 1581</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>1561, 1564</t>
+  </si>
+  <si>
+    <t>1582, 1583</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>1609, 1616, 1617</t>
+  </si>
+  <si>
+    <t>1610, 1611, 1612</t>
+  </si>
+  <si>
+    <t>1559, 1560</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>1592</t>
   </si>
   <si>
     <t>Allgemein_VRF</t>
@@ -535,6 +715,9 @@
     <t>Aussenbereich_ALL</t>
   </si>
   <si>
+    <t>Aussenbereich_ASP</t>
+  </si>
+  <si>
     <t>Aussenbereich_BUF</t>
   </si>
   <si>
@@ -544,18 +727,15 @@
     <t>Aussenbereich_PAA</t>
   </si>
   <si>
+    <t>Aussenbereich_PAG</t>
+  </si>
+  <si>
     <t>Aussenbereich_PAK</t>
   </si>
   <si>
-    <t>Aussenbereich_PPA</t>
-  </si>
-  <si>
     <t>Aussenbereich_UUF</t>
   </si>
   <si>
-    <t>Aussenbereich_VEL_L</t>
-  </si>
-  <si>
     <t>Betreuung_AUF_G</t>
   </si>
   <si>
@@ -568,18 +748,45 @@
     <t>Betreuung_KUC</t>
   </si>
   <si>
+    <t>Betreuung_KUE</t>
+  </si>
+  <si>
+    <t>Betreuung_KUL</t>
+  </si>
+  <si>
+    <t>Betreuung_KUW</t>
+  </si>
+  <si>
     <t>Betreuung_MEN</t>
   </si>
   <si>
+    <t>Betreuung_RKU</t>
+  </si>
+  <si>
+    <t>Betreuung_VOR</t>
+  </si>
+  <si>
+    <t>Betreuung_WCD</t>
+  </si>
+  <si>
+    <t>Betreuung_WCH</t>
+  </si>
+  <si>
     <t>Betreuung_WCR</t>
   </si>
   <si>
     <t>Funktionsfläche_HTR_E</t>
   </si>
   <si>
+    <t>Funktionsfläche_HTR_K</t>
+  </si>
+  <si>
     <t>Funktionsfläche_HTR_L</t>
   </si>
   <si>
+    <t>Funktionsfläche_HTR_S</t>
+  </si>
+  <si>
     <t>GrossArea</t>
   </si>
   <si>
@@ -592,9 +799,27 @@
     <t>Hausdienst_CON</t>
   </si>
   <si>
+    <t>Hausdienst_GRP</t>
+  </si>
+  <si>
+    <t>Hausdienst_HRR</t>
+  </si>
+  <si>
+    <t>Hausdienst_RRG</t>
+  </si>
+  <si>
+    <t>IfcSpace</t>
+  </si>
+  <si>
     <t>Luftraum_LUF</t>
   </si>
   <si>
+    <t>Sonstige Umgebung_AVF</t>
+  </si>
+  <si>
+    <t>Sonstige Umgebung_TRHa</t>
+  </si>
+  <si>
     <t>Sportbereich_AGS</t>
   </si>
   <si>
@@ -617,9 +842,6 @@
   </si>
   <si>
     <t>Sportbereich_SPH</t>
-  </si>
-  <si>
-    <t>Sportbereich_VSR</t>
   </si>
   <si>
     <t>Sportbereich_WCK</t>
@@ -1007,10 +1229,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1056,90 +1278,102 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H2" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="K2">
-        <v>224.5725255</v>
+        <v>80.0549015</v>
       </c>
       <c r="L2">
-        <v>44.5051765</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>89.90167199999999</v>
+        <v>36.1246745</v>
       </c>
       <c r="N2">
-        <v>29.57241</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>60.593267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>43.930227</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="H3" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="K3">
-        <v>517.6972254999999</v>
+        <v>311.9691595</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>311.9691595</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1148,186 +1382,210 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>517.6972254999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="K4">
-        <v>1700.4758295</v>
+        <v>51.829968</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>51.829968</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1700.4758295</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="K5">
-        <v>149.781966</v>
+        <v>424.5565245</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>424.5565245</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>149.781966</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H6" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="K6">
-        <v>1405.3773035</v>
+        <v>438.508773</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>438.508773</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1105.1280485</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>300.249255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="K7">
-        <v>192.714786</v>
+        <v>1503.512742</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1503.512742</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1336,183 +1594,207 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>192.714786</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="K8">
-        <v>12.501687</v>
+        <v>73.743488</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>73.743488</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>12.501687</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="K9">
-        <v>1624.359665</v>
+        <v>450.5657505</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>450.5657505</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1624.359665</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="K10">
-        <v>6.683796</v>
+        <v>1079.9930175</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1079.9930175</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>6.683796</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K11">
-        <v>69.21536450000001</v>
+        <v>97.30420100000001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1521,45 +1803,51 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>69.21536450000001</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>97.30420100000001</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="H12" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="K12">
-        <v>58.270363</v>
+        <v>48.652963</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1568,45 +1856,51 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>58.270363</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>48.652963</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="K13">
-        <v>19.561439</v>
+        <v>18.100976</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1615,45 +1909,51 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>19.561439</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>18.100976</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="H14" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="K14">
-        <v>47.7329045</v>
+        <v>52.0864025</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1662,45 +1962,51 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>47.7329045</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>52.0864025</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="H15" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="K15">
-        <v>77.20383200000001</v>
+        <v>7.1488355</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1709,45 +2015,51 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>77.20383200000001</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>7.1488355</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="K16">
-        <v>9.490406999999999</v>
+        <v>5.3788925</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1756,215 +2068,263 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>9.490406999999999</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>5.3788925</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="K17">
-        <v>60.963572</v>
+        <v>6.7310435</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>60.963572</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>6.7310435</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>247</v>
+      </c>
+      <c r="K18">
+        <v>120.5809505</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>37.01257</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>83.5683805</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
         <v>103</v>
       </c>
-      <c r="H18" t="s">
-        <v>145</v>
-      </c>
-      <c r="I18">
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I19">
         <v>1</v>
       </c>
-      <c r="J18" t="s">
-        <v>187</v>
-      </c>
-      <c r="K18">
-        <v>15.56272</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>15.56272</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" t="s">
-        <v>146</v>
-      </c>
-      <c r="I19">
-        <v>8</v>
-      </c>
       <c r="J19" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="K19">
-        <v>3509.7219105</v>
+        <v>6.217429</v>
       </c>
       <c r="L19">
-        <v>1212.806694</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>1357.0385225</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>829.1200164999999</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>110.7566775</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>6.217429</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>86</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" t="s">
+        <v>108</v>
       </c>
       <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K20">
+        <v>113.1970605</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>113.1970605</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
         <v>86</v>
       </c>
-      <c r="G20" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20">
-        <v>16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>189</v>
-      </c>
-      <c r="K20">
-        <v>5148.04254</v>
-      </c>
-      <c r="L20">
-        <v>2425.613388</v>
-      </c>
-      <c r="M20">
-        <v>1501.2657815</v>
-      </c>
-      <c r="N20">
-        <v>1092.1129905</v>
-      </c>
-      <c r="O20">
-        <v>129.05038</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>65</v>
-      </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="K21">
-        <v>16.94712</v>
+        <v>6.3144375</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1973,45 +2333,51 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>16.94712</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>6.3144375</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="K22">
-        <v>9.108307999999999</v>
+        <v>6.54133</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -2020,39 +2386,51 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>9.108307999999999</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>6.54133</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="K23">
-        <v>26.544178</v>
+        <v>3.356215</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2061,139 +2439,157 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>26.544178</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>3.356215</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>253</v>
+      </c>
+      <c r="K24">
+        <v>21.840469</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>21.840469</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" t="s">
+        <v>198</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>254</v>
+      </c>
+      <c r="K25">
+        <v>64.9122115</v>
+      </c>
+      <c r="L25">
+        <v>45.3332775</v>
+      </c>
+      <c r="M25">
+        <v>19.578934</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
         <v>75</v>
       </c>
-      <c r="E24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s">
         <v>109</v>
       </c>
-      <c r="H24" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24">
-        <v>2</v>
-      </c>
-      <c r="J24" t="s">
-        <v>192</v>
-      </c>
-      <c r="K24">
-        <v>895.986936</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>895.986936</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25" t="s">
-        <v>193</v>
-      </c>
-      <c r="K25">
-        <v>9.990109</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>9.990109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G26" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="H26" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="K26">
-        <v>35.498551</v>
+        <v>108.9698425</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2202,471 +2598,495 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>35.498551</v>
+        <v>108.9698425</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>256</v>
+      </c>
+      <c r="K27">
+        <v>49.6842235</v>
+      </c>
+      <c r="L27">
+        <v>49.6842235</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H28" t="s">
+        <v>201</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28">
+        <v>3955.6860015</v>
+      </c>
+      <c r="L28">
+        <v>776.0154415</v>
+      </c>
+      <c r="M28">
+        <v>842.3266265</v>
+      </c>
+      <c r="N28">
+        <v>124.129938</v>
+      </c>
+      <c r="O28">
+        <v>743.6416495</v>
+      </c>
+      <c r="P28">
+        <v>741.0075265</v>
+      </c>
+      <c r="Q28">
+        <v>728.5648195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" t="s">
+        <v>146</v>
+      </c>
+      <c r="H29" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29">
+        <v>13</v>
+      </c>
+      <c r="J29" t="s">
+        <v>258</v>
+      </c>
+      <c r="K29">
+        <v>5742.9247415</v>
+      </c>
+      <c r="L29">
+        <v>782.9935634999999</v>
+      </c>
+      <c r="M29">
+        <v>2492.593737</v>
+      </c>
+      <c r="N29">
+        <v>248.252202</v>
+      </c>
+      <c r="O29">
+        <v>743.6416495</v>
+      </c>
+      <c r="P29">
+        <v>741.0075265</v>
+      </c>
+      <c r="Q29">
+        <v>734.436063</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" t="s">
+        <v>147</v>
+      </c>
+      <c r="H30" t="s">
+        <v>203</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>259</v>
+      </c>
+      <c r="K30">
+        <v>13.877304</v>
+      </c>
+      <c r="L30">
+        <v>13.877304</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" t="s">
+        <v>204</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>260</v>
+      </c>
+      <c r="K31">
+        <v>11.656106</v>
+      </c>
+      <c r="L31">
+        <v>11.656106</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" t="s">
+        <v>205</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>261</v>
+      </c>
+      <c r="K32">
+        <v>12.8353175</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>12.8353175</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" t="s">
+        <v>206</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>262</v>
+      </c>
+      <c r="K33">
+        <v>25.036691</v>
+      </c>
+      <c r="L33">
+        <v>25.036691</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" t="s">
+        <v>151</v>
+      </c>
+      <c r="H34" t="s">
+        <v>207</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" t="s">
+        <v>263</v>
+      </c>
+      <c r="K34">
+        <v>12.527038</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>6.5319785</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>5.9950595</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="B35" t="s">
         <v>73</v>
       </c>
-      <c r="E27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" t="s">
-        <v>154</v>
-      </c>
-      <c r="I27">
-        <v>2</v>
-      </c>
-      <c r="J27" t="s">
-        <v>195</v>
-      </c>
-      <c r="K27">
-        <v>32.532022</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>32.532022</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" t="s">
-        <v>113</v>
-      </c>
-      <c r="H28" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28">
-        <v>4</v>
-      </c>
-      <c r="J28" t="s">
-        <v>196</v>
-      </c>
-      <c r="K28">
-        <v>172.302794</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>172.302794</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
         <v>114</v>
       </c>
-      <c r="H29" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>197</v>
-      </c>
-      <c r="K29">
-        <v>13.314032</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>13.314032</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" t="s">
-        <v>115</v>
-      </c>
-      <c r="H30" t="s">
-        <v>157</v>
-      </c>
-      <c r="I30">
-        <v>2</v>
-      </c>
-      <c r="J30" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30">
-        <v>34.7560375</v>
-      </c>
-      <c r="L30">
-        <v>9.675238999999999</v>
-      </c>
-      <c r="M30">
-        <v>25.0807985</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" t="s">
-        <v>116</v>
-      </c>
-      <c r="H31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31" t="s">
-        <v>199</v>
-      </c>
-      <c r="K31">
-        <v>179.2507285</v>
-      </c>
-      <c r="L31">
-        <v>179.2507285</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32">
-        <v>2</v>
-      </c>
-      <c r="J32" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32">
-        <v>895.986936</v>
-      </c>
-      <c r="L32">
-        <v>895.986936</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G33" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" t="s">
-        <v>160</v>
-      </c>
-      <c r="I33">
-        <v>2</v>
-      </c>
-      <c r="J33" t="s">
-        <v>201</v>
-      </c>
-      <c r="K33">
-        <v>11.072026</v>
-      </c>
-      <c r="L33">
-        <v>11.072026</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" t="s">
-        <v>161</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34" t="s">
-        <v>202</v>
-      </c>
-      <c r="K34">
-        <v>17.154349</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>17.154349</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E35" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" t="s">
-        <v>83</v>
-      </c>
       <c r="G35" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="K35">
-        <v>17.1529545</v>
+        <v>482.7840085</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>482.7840085</v>
       </c>
       <c r="N35">
-        <v>17.1529545</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="B36" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="K36">
-        <v>9.07253</v>
+        <v>462.949212</v>
       </c>
       <c r="L36">
-        <v>9.07253</v>
+        <v>462.949212</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2677,87 +3097,99 @@
       <c r="O36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="H37" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J37" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="K37">
-        <v>17.776442</v>
+        <v>618.5320614999998</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>7.00499</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>127.5777285</v>
       </c>
       <c r="N37">
-        <v>17.776442</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>7.00499</v>
+      </c>
+      <c r="P37">
+        <v>7.00499</v>
+      </c>
+      <c r="Q37">
+        <v>469.939363</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G38" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="H38" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="K38">
-        <v>12.942644</v>
+        <v>92.00158949999999</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2766,244 +3198,1022 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>12.942644</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>27.064</v>
+      </c>
+      <c r="P38">
+        <v>29.1196845</v>
+      </c>
+      <c r="Q38">
+        <v>35.817905</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" t="s">
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G39" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="H39" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="K39">
-        <v>36.386102</v>
+        <v>38.1497405</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>38.1497405</v>
       </c>
       <c r="N39">
-        <v>36.386102</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" t="s">
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="H40" t="s">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="K40">
-        <v>17.781138</v>
+        <v>16.4718365</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>16.4718365</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>17.781138</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" t="s">
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="H41" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="I41">
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="K41">
-        <v>36.385945</v>
+        <v>62.0861185</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>62.0861185</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>36.385945</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" t="s">
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="H42" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="K42">
-        <v>91.8780515</v>
+        <v>30.587292</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>15.293646</v>
       </c>
       <c r="N42">
-        <v>91.8780515</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="P42">
+        <v>15.293646</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" t="s">
         <v>54</v>
       </c>
       <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" t="s">
+        <v>112</v>
+      </c>
+      <c r="F43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" t="s">
+        <v>160</v>
+      </c>
+      <c r="H43" t="s">
+        <v>216</v>
+      </c>
+      <c r="I43">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43">
+        <v>152.223724</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>76.111862</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>76.111862</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" t="s">
+        <v>114</v>
+      </c>
+      <c r="G44" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" t="s">
+        <v>217</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44">
+        <v>8.992677</v>
+      </c>
+      <c r="L44">
+        <v>8.992677</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45" t="s">
+        <v>273</v>
+      </c>
+      <c r="K45">
+        <v>22.39557</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>11.197785</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>11.197785</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
         <v>57</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" t="s">
+        <v>114</v>
+      </c>
+      <c r="G46" t="s">
+        <v>163</v>
+      </c>
+      <c r="H46" t="s">
+        <v>219</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46" t="s">
+        <v>274</v>
+      </c>
+      <c r="K46">
+        <v>174.111751</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>87.0558755</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>87.0558755</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" t="s">
+        <v>164</v>
+      </c>
+      <c r="H47" t="s">
+        <v>220</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" t="s">
+        <v>275</v>
+      </c>
+      <c r="K47">
+        <v>462.934373</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>462.934373</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" t="s">
+        <v>114</v>
+      </c>
+      <c r="G48" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" t="s">
+        <v>221</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48" t="s">
+        <v>276</v>
+      </c>
+      <c r="K48">
+        <v>20.548728</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>6.849576</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>6.849576</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>6.849576</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" t="s">
+        <v>222</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+      <c r="J49" t="s">
+        <v>277</v>
+      </c>
+      <c r="K49">
+        <v>18.560214</v>
+      </c>
+      <c r="L49">
+        <v>6.849576</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>4.861062</v>
+      </c>
+      <c r="P49">
+        <v>6.849576</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F50" t="s">
+        <v>114</v>
+      </c>
+      <c r="G50" t="s">
+        <v>167</v>
+      </c>
+      <c r="H50" t="s">
+        <v>223</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50" t="s">
+        <v>278</v>
+      </c>
+      <c r="K50">
+        <v>8.733451000000001</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>4.3667255</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>4.3667255</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F51" t="s">
+        <v>114</v>
+      </c>
+      <c r="G51" t="s">
+        <v>168</v>
+      </c>
+      <c r="H51" t="s">
+        <v>224</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51" t="s">
+        <v>279</v>
+      </c>
+      <c r="K51">
+        <v>18.09956</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>18.09956</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" t="s">
+        <v>113</v>
+      </c>
+      <c r="F52" t="s">
+        <v>114</v>
+      </c>
+      <c r="G52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H52" t="s">
+        <v>225</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>280</v>
+      </c>
+      <c r="K52">
+        <v>21.1748135</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>21.1748135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" t="s">
+        <v>113</v>
+      </c>
+      <c r="F53" t="s">
+        <v>114</v>
+      </c>
+      <c r="G53" t="s">
+        <v>170</v>
+      </c>
+      <c r="H53" t="s">
+        <v>226</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>281</v>
+      </c>
+      <c r="K53">
+        <v>37.0116145</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>37.0116145</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" t="s">
         <v>65</v>
       </c>
-      <c r="D43" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" t="s">
-        <v>82</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="B54" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" t="s">
+        <v>113</v>
+      </c>
+      <c r="F54" t="s">
+        <v>114</v>
+      </c>
+      <c r="G54" t="s">
+        <v>171</v>
+      </c>
+      <c r="H54" t="s">
+        <v>227</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>282</v>
+      </c>
+      <c r="K54">
+        <v>18.096385</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>18.096385</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" t="s">
+        <v>114</v>
+      </c>
+      <c r="G55" t="s">
+        <v>172</v>
+      </c>
+      <c r="H55" t="s">
+        <v>228</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
+        <v>283</v>
+      </c>
+      <c r="K55">
+        <v>37.0116145</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>37.0116145</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" t="s">
         <v>83</v>
       </c>
-      <c r="G43" t="s">
-        <v>128</v>
-      </c>
-      <c r="H43" t="s">
-        <v>170</v>
-      </c>
-      <c r="I43">
+      <c r="C56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" t="s">
+        <v>113</v>
+      </c>
+      <c r="F56" t="s">
+        <v>114</v>
+      </c>
+      <c r="G56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" t="s">
+        <v>229</v>
+      </c>
+      <c r="I56">
         <v>1</v>
       </c>
-      <c r="J43" t="s">
-        <v>211</v>
-      </c>
-      <c r="K43">
-        <v>55.058047</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>55.058047</v>
-      </c>
-      <c r="O43">
+      <c r="J56" t="s">
+        <v>284</v>
+      </c>
+      <c r="K56">
+        <v>82.35027049999999</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>82.35027049999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F57" t="s">
+        <v>114</v>
+      </c>
+      <c r="G57" t="s">
+        <v>174</v>
+      </c>
+      <c r="H57" t="s">
+        <v>230</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>285</v>
+      </c>
+      <c r="K57">
+        <v>48.657669</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>48.657669</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
         <v>0</v>
       </c>
     </row>
